--- a/data/trans_camb/MCS12_SP_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 16,77</t>
+          <t>6,62; 17,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 15,68</t>
+          <t>4,68; 15,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 6,21</t>
+          <t>-5,28; 5,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,89; 24,06</t>
+          <t>13,71; 23,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 14,19</t>
+          <t>3,69; 14,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 4,47</t>
+          <t>-6,38; 3,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,01; 18,69</t>
+          <t>11,27; 18,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 13,51</t>
+          <t>6,16; 13,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,84</t>
+          <t>-3,56; 3,64</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,98; 47,16</t>
+          <t>16,04; 49,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,38; 44,58</t>
+          <t>11,57; 44,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 17,78</t>
+          <t>-13,24; 16,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,57; 53,66</t>
+          <t>27,05; 53,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,95; 32,05</t>
+          <t>7,24; 32,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 10,11</t>
+          <t>-12,55; 7,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,76; 45,66</t>
+          <t>25,59; 46,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,77; 32,97</t>
+          <t>13,75; 34,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 9,39</t>
+          <t>-7,85; 8,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 9,51</t>
+          <t>0,26; 9,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 7,53</t>
+          <t>-1,11; 7,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 0,18</t>
+          <t>-28,81; -0,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 6,1</t>
+          <t>-2,71; 6,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 2,45</t>
+          <t>-7,32; 1,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,11; -3,89</t>
+          <t>-12,04; -3,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 7,01</t>
+          <t>0,07; 6,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 3,79</t>
+          <t>-2,71; 3,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,02; -3,69</t>
+          <t>-23,93; -3,28</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 23,48</t>
+          <t>0,56; 23,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 18,55</t>
+          <t>-2,43; 18,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,27; 0,52</t>
+          <t>-60,92; -1,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 11,27</t>
+          <t>-4,71; 12,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 4,64</t>
+          <t>-12,42; 3,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -7,06</t>
+          <t>-20,48; -6,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 14,55</t>
+          <t>0,15; 13,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 7,89</t>
+          <t>-5,26; 7,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-46,15; -7,44</t>
+          <t>-47,54; -6,79</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 6,96</t>
+          <t>-3,89; 7,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,87</t>
+          <t>-5,97; 4,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 2,47</t>
+          <t>-8,75; 2,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 9,87</t>
+          <t>-0,43; 9,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -0,24</t>
+          <t>-10,47; -0,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 25,23</t>
+          <t>-8,67; 26,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 6,86</t>
+          <t>-0,62; 7,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 0,2</t>
+          <t>-7,32; 0,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 19,12</t>
+          <t>-6,32; 21,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 16,97</t>
+          <t>-8,18; 17,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 9,27</t>
+          <t>-12,9; 11,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 6,36</t>
+          <t>-18,87; 6,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 18,53</t>
+          <t>-0,74; 18,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -0,47</t>
+          <t>-18,45; -0,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 48,06</t>
+          <t>-15,66; 49,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 14,67</t>
+          <t>-1,19; 15,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 0,43</t>
+          <t>-14,4; 0,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 40,64</t>
+          <t>-12,67; 46,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,63; 10,42</t>
+          <t>1,22; 10,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 11,65</t>
+          <t>2,16; 11,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 2,74</t>
+          <t>-7,17; 2,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 13,06</t>
+          <t>3,88; 12,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,47</t>
+          <t>-1,29; 7,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 10,49</t>
+          <t>-3,13; 10,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,52</t>
+          <t>3,94; 10,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,13</t>
+          <t>2,09; 8,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 5,0</t>
+          <t>-3,75; 5,7</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 23,39</t>
+          <t>2,23; 23,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,53; 26,09</t>
+          <t>4,29; 25,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 6,13</t>
+          <t>-14,64; 5,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,71; 24,34</t>
+          <t>6,85; 23,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 13,93</t>
+          <t>-2,46; 13,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 18,93</t>
+          <t>-5,56; 20,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,95; 21,07</t>
+          <t>7,39; 20,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,26; 16,14</t>
+          <t>4,05; 16,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 9,95</t>
+          <t>-7,07; 11,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,15</t>
+          <t>3,34; 8,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 7,57</t>
+          <t>2,39; 7,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,06; -0,96</t>
+          <t>-13,71; -0,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,96</t>
+          <t>5,38; 9,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,95</t>
+          <t>-1,74; 3,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 8,24</t>
+          <t>-4,2; 7,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,56</t>
+          <t>5,19; 8,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,73</t>
+          <t>1,06; 4,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 2,0</t>
+          <t>-7,29; 2,58</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,29; 19,58</t>
+          <t>7,57; 19,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5,75; 17,82</t>
+          <t>5,38; 17,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-33,67; -2,26</t>
+          <t>-31,02; -1,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9,41; 18,95</t>
+          <t>9,56; 18,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 5,59</t>
+          <t>-3,09; 6,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 15,27</t>
+          <t>-7,69; 14,62</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,18; 17,89</t>
+          <t>10,41; 18,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,93</t>
+          <t>2,11; 9,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 4,23</t>
+          <t>-14,96; 5,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 17,14</t>
+          <t>5,61; 16,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 15,77</t>
+          <t>4,94; 15,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 5,83</t>
+          <t>-4,71; 5,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,71; 23,74</t>
+          <t>13,27; 23,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 14,48</t>
+          <t>4,03; 14,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 3,52</t>
+          <t>-5,88; 4,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,27; 18,98</t>
+          <t>11,46; 19,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 13,97</t>
+          <t>5,74; 13,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,64</t>
+          <t>-3,65; 3,9</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-1,64%</t>
+          <t>-1,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,01%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,04; 49,77</t>
+          <t>13,72; 46,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,57; 44,51</t>
+          <t>12,18; 44,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 16,29</t>
+          <t>-11,66; 15,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,05; 53,0</t>
+          <t>26,56; 52,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,24; 32,02</t>
+          <t>7,96; 31,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 7,7</t>
+          <t>-11,47; 9,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,59; 46,75</t>
+          <t>25,28; 46,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 34,12</t>
+          <t>12,67; 33,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 8,98</t>
+          <t>-8,24; 9,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-10,12</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,73</t>
+          <t>-7,32</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-9,82</t>
+          <t>-4,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 9,48</t>
+          <t>0,32; 9,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,77</t>
+          <t>-1,09; 8,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,81; -0,52</t>
+          <t>-5,7; 3,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 6,58</t>
+          <t>-3,23; 6,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 1,79</t>
+          <t>-7,17; 2,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,04; -3,46</t>
+          <t>-11,62; -3,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,4</t>
+          <t>-0,07; 6,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,56</t>
+          <t>-2,91; 3,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-23,93; -3,28</t>
+          <t>-7,12; -0,87</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-23,51%</t>
+          <t>-2,8%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-13,7%</t>
+          <t>-12,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-19,72%</t>
+          <t>-8,54%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 23,3</t>
+          <t>0,54; 22,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 18,79</t>
+          <t>-2,68; 19,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,92; -1,14</t>
+          <t>-12,73; 9,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 12,03</t>
+          <t>-5,43; 11,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 3,45</t>
+          <t>-12,4; 3,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,48; -6,51</t>
+          <t>-19,76; -5,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 13,29</t>
+          <t>-0,25; 13,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 7,48</t>
+          <t>-5,7; 7,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,54; -6,79</t>
+          <t>-14,0; -1,85</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,12</t>
+          <t>-3,48</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>-4,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>-3,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 7,1</t>
+          <t>-3,64; 7,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 4,68</t>
+          <t>-6,25; 4,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 2,92</t>
+          <t>-9,68; 1,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 9,61</t>
+          <t>-0,73; 9,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -0,44</t>
+          <t>-10,85; -0,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 26,1</t>
+          <t>-9,71; 0,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 7,16</t>
+          <t>-0,58; 7,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 0,09</t>
+          <t>-7,24; 0,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 21,77</t>
+          <t>-7,59; -0,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-7,14%</t>
+          <t>-7,96%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>-7,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>-7,95%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 17,39</t>
+          <t>-8,11; 18,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 11,47</t>
+          <t>-13,49; 10,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 6,92</t>
+          <t>-20,74; 3,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 18,24</t>
+          <t>-1,33; 17,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,45; -0,84</t>
+          <t>-18,8; -1,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 49,18</t>
+          <t>-16,76; 0,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 15,19</t>
+          <t>-1,21; 15,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 0,17</t>
+          <t>-14,18; 0,73</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 46,88</t>
+          <t>-14,88; -0,76</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,39</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-1,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,51</t>
+          <t>1,67; 10,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,45</t>
+          <t>2,89; 11,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 2,4</t>
+          <t>-5,92; 3,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,78</t>
+          <t>4,18; 13,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 7,32</t>
+          <t>-1,41; 7,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 10,92</t>
+          <t>-5,13; 3,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 10,12</t>
+          <t>4,06; 10,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,28</t>
+          <t>1,87; 8,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,7</t>
+          <t>-4,12; 2,04</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-5,09%</t>
+          <t>-3,02%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>-1,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-0,12%</t>
+          <t>-2,06%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 23,53</t>
+          <t>3,41; 22,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,29; 25,75</t>
+          <t>5,8; 25,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 5,43</t>
+          <t>-12,1; 7,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,85; 23,9</t>
+          <t>7,32; 24,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 13,36</t>
+          <t>-2,51; 13,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 20,55</t>
+          <t>-8,79; 5,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,39; 20,37</t>
+          <t>7,65; 20,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,05; 16,57</t>
+          <t>3,56; 16,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 11,33</t>
+          <t>-7,69; 4,0</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-4,58</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-2,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,3</t>
+          <t>3,3; 8,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,51</t>
+          <t>2,48; 7,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -0,66</t>
+          <t>-3,87; 1,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,88</t>
+          <t>5,52; 10,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,26</t>
+          <t>-1,98; 2,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 7,91</t>
+          <t>-5,84; -1,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,68</t>
+          <t>4,82; 8,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,52</t>
+          <t>0,94; 4,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,58</t>
+          <t>-4,17; -0,77</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-10,6%</t>
+          <t>-3,18%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-0,7%</t>
+          <t>-6,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-4,82%</t>
+          <t>-4,83%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,57; 19,9</t>
+          <t>7,34; 19,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5,38; 17,95</t>
+          <t>5,5; 17,51</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-31,02; -1,58</t>
+          <t>-8,77; 2,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9,56; 18,62</t>
+          <t>9,96; 19,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 6,15</t>
+          <t>-3,57; 5,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 14,62</t>
+          <t>-10,48; -2,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,41; 18,21</t>
+          <t>9,69; 17,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,39</t>
+          <t>1,87; 9,22</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 5,36</t>
+          <t>-8,37; -1,58</t>
         </is>
       </c>
     </row>
